--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7989,6 +7989,2625 @@
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129464365</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91996</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>509739</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6718995</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129464976</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>509842</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6718979</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129458615</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Långsberget, Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>509291</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6718937</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På tall.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129464423</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91841</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>658</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>509741</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6718995</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129476786</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91996</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>509746</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6718981</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129458905</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98710</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>509314</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6718886</v>
+      </c>
+      <c r="S71" t="n">
+        <v>6</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Johan Hedberg</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Johan Hedberg</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129457884</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Långsberget, Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>509318</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6718896</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129459431</v>
+      </c>
+      <c r="B73" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Långsberget, Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>509267</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6718938</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129458644</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91507</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Långsberget, Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>509309</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6718945</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129464831</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>509874</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6719068</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, inte jätte gamla.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129462456</v>
+      </c>
+      <c r="B76" t="n">
+        <v>98710</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Långsberget, Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>509476</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6719032</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129476788</v>
+      </c>
+      <c r="B77" t="n">
+        <v>92863</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>509550</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6719093</v>
+      </c>
+      <c r="S77" t="n">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>25cm bredd</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129464986</v>
+      </c>
+      <c r="B78" t="n">
+        <v>98710</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Lindbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>509694</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6719079</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Johan Hedberg</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Johan Hedberg</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129460153</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>509450</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6718977</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Johan Hedberg</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Johan Hedberg</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129463357</v>
+      </c>
+      <c r="B80" t="n">
+        <v>91996</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>509719</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6719096</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129465090</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91996</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>509695</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6718938</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129465133</v>
+      </c>
+      <c r="B82" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Lindbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>509707</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6719050</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Betade tallar 3 st</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Johan Hedberg</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Johan Hedberg</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129462748</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98710</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>509404</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6719022</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Johan Hedberg</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Johan Hedberg</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129463017</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>509454</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6719013</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Johan Hedberg</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Johan Hedberg</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129462703</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Långsberget, Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>509520</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6719068</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129476790</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>509698</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6718999</v>
+      </c>
+      <c r="S86" t="n">
+        <v>1</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>129465440</v>
+      </c>
+      <c r="B87" t="n">
+        <v>98710</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Lindbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>509588</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6718900</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Johan Hedberg</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Johan Hedberg</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>129463311</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>509717</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6719091</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129457466</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Långsberget, Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>509363</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6718877</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På tall.</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -7991,45 +7991,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129464365</v>
+        <v>129458615</v>
       </c>
       <c r="B66" t="n">
-        <v>91996</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509739</v>
+        <v>509291</v>
       </c>
       <c r="R66" t="n">
-        <v>6718995</v>
+        <v>6718937</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8061,7 +8066,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8071,12 +8076,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8106,7 +8111,7 @@
         <v>129464976</v>
       </c>
       <c r="B67" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8210,50 +8215,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129458615</v>
+        <v>129464365</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>91998</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>509291</v>
+        <v>509739</v>
       </c>
       <c r="R68" t="n">
-        <v>6718937</v>
+        <v>6718995</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8330,7 +8330,7 @@
         <v>129464423</v>
       </c>
       <c r="B69" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>129476786</v>
       </c>
       <c r="B70" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8540,57 +8540,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129458905</v>
+        <v>129459431</v>
       </c>
       <c r="B71" t="n">
-        <v>98710</v>
+        <v>5177</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509314</v>
+        <v>509267</v>
       </c>
       <c r="R71" t="n">
-        <v>6718886</v>
+        <v>6718938</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8617,9 +8613,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8634,60 +8640,69 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129457884</v>
+        <v>129458905</v>
       </c>
       <c r="B72" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509318</v>
+        <v>509314</v>
       </c>
       <c r="R72" t="n">
-        <v>6718896</v>
+        <v>6718886</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8714,24 +8729,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8746,62 +8746,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129459431</v>
+        <v>129457884</v>
       </c>
       <c r="B73" t="n">
-        <v>5177</v>
+        <v>79044</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>509267</v>
+        <v>509318</v>
       </c>
       <c r="R73" t="n">
-        <v>6718938</v>
+        <v>6718896</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8833,7 +8828,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8843,7 +8838,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8870,45 +8870,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129458644</v>
+        <v>129464831</v>
       </c>
       <c r="B74" t="n">
-        <v>91507</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>509309</v>
+        <v>509874</v>
       </c>
       <c r="R74" t="n">
-        <v>6718945</v>
+        <v>6719068</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8940,7 +8945,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8950,7 +8955,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8977,50 +8987,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129464831</v>
+        <v>129458644</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>91509</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>509874</v>
+        <v>509309</v>
       </c>
       <c r="R75" t="n">
-        <v>6719068</v>
+        <v>6718945</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9052,7 +9057,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9062,12 +9067,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, inte jätte gamla.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9094,62 +9094,51 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129462456</v>
+        <v>129476788</v>
       </c>
       <c r="B76" t="n">
-        <v>98710</v>
+        <v>92865</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>509476</v>
+        <v>509550</v>
       </c>
       <c r="R76" t="n">
-        <v>6719032</v>
+        <v>6719093</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9176,24 +9165,14 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>25cm bredd</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9202,69 +9181,81 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129476788</v>
+        <v>129462456</v>
       </c>
       <c r="B77" t="n">
-        <v>92863</v>
+        <v>98712</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>509550</v>
+        <v>509476</v>
       </c>
       <c r="R77" t="n">
-        <v>6719093</v>
+        <v>6719032</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9291,14 +9282,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>25cm bredd</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9307,19 +9308,18 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9329,7 +9329,7 @@
         <v>129464986</v>
       </c>
       <c r="B78" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>129460153</v>
       </c>
       <c r="B79" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9538,45 +9538,55 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129463357</v>
+        <v>129465133</v>
       </c>
       <c r="B80" t="n">
-        <v>91996</v>
+        <v>56917</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>509719</v>
+        <v>509707</v>
       </c>
       <c r="R80" t="n">
-        <v>6719096</v>
+        <v>6719050</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9606,19 +9616,14 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>13:29</t>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Betade tallar 3 st</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9633,22 +9638,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129465090</v>
+        <v>129463357</v>
       </c>
       <c r="B81" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9680,10 +9685,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>509695</v>
+        <v>509719</v>
       </c>
       <c r="R81" t="n">
-        <v>6718938</v>
+        <v>6719096</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9715,7 +9720,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9725,7 +9730,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9752,55 +9757,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129465133</v>
+        <v>129465090</v>
       </c>
       <c r="B82" t="n">
-        <v>56917</v>
+        <v>91998</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>509707</v>
+        <v>509695</v>
       </c>
       <c r="R82" t="n">
-        <v>6719050</v>
+        <v>6718938</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9830,14 +9825,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Betade tallar 3 st</t>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9852,12 +9852,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9867,7 +9867,7 @@
         <v>129462748</v>
       </c>
       <c r="B83" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9970,10 +9970,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129463017</v>
+        <v>129462703</v>
       </c>
       <c r="B84" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9981,39 +9981,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>509454</v>
+        <v>509520</v>
       </c>
       <c r="R84" t="n">
-        <v>6719013</v>
+        <v>6719068</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10043,9 +10038,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10060,22 +10070,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129462703</v>
+        <v>129463017</v>
       </c>
       <c r="B85" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10083,34 +10093,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>509520</v>
+        <v>509454</v>
       </c>
       <c r="R85" t="n">
-        <v>6719068</v>
+        <v>6719013</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10140,24 +10155,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10172,12 +10172,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10187,7 +10187,7 @@
         <v>129476790</v>
       </c>
       <c r="B86" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10281,57 +10281,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129465440</v>
+        <v>129463311</v>
       </c>
       <c r="B87" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>509588</v>
+        <v>509717</v>
       </c>
       <c r="R87" t="n">
-        <v>6718900</v>
+        <v>6719091</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10361,75 +10349,96 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129463311</v>
+        <v>129465440</v>
       </c>
       <c r="B88" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>509717</v>
+        <v>509588</v>
       </c>
       <c r="R88" t="n">
-        <v>6719091</v>
+        <v>6718900</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10459,39 +10468,30 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10501,7 +10501,7 @@
         <v>129457466</v>
       </c>
       <c r="B89" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -7991,50 +7991,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129458615</v>
+        <v>129464365</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>92002</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509291</v>
+        <v>509739</v>
       </c>
       <c r="R66" t="n">
-        <v>6718937</v>
+        <v>6718995</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8066,7 +8061,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8076,12 +8071,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8215,45 +8210,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129464365</v>
+        <v>129458615</v>
       </c>
       <c r="B68" t="n">
-        <v>91998</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>509739</v>
+        <v>509291</v>
       </c>
       <c r="R68" t="n">
-        <v>6718995</v>
+        <v>6718937</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8330,7 +8330,7 @@
         <v>129464423</v>
       </c>
       <c r="B69" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>129476786</v>
       </c>
       <c r="B70" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>129458905</v>
       </c>
       <c r="B72" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8870,50 +8870,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129464831</v>
+        <v>129458644</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>91513</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>509874</v>
+        <v>509309</v>
       </c>
       <c r="R74" t="n">
-        <v>6719068</v>
+        <v>6718945</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8945,7 +8940,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8955,12 +8950,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, inte jätte gamla.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8987,45 +8977,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129458644</v>
+        <v>129464831</v>
       </c>
       <c r="B75" t="n">
-        <v>91509</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>509309</v>
+        <v>509874</v>
       </c>
       <c r="R75" t="n">
-        <v>6718945</v>
+        <v>6719068</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9057,7 +9052,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9067,7 +9062,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9097,7 +9097,7 @@
         <v>129476788</v>
       </c>
       <c r="B76" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>129462456</v>
       </c>
       <c r="B77" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>129464986</v>
       </c>
       <c r="B78" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9538,55 +9538,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129465133</v>
+        <v>129463357</v>
       </c>
       <c r="B80" t="n">
-        <v>56917</v>
+        <v>92002</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>509707</v>
+        <v>509719</v>
       </c>
       <c r="R80" t="n">
-        <v>6719050</v>
+        <v>6719096</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9616,14 +9606,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Betade tallar 3 st</t>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9638,22 +9633,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129463357</v>
+        <v>129465090</v>
       </c>
       <c r="B81" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9685,10 +9680,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>509719</v>
+        <v>509695</v>
       </c>
       <c r="R81" t="n">
-        <v>6719096</v>
+        <v>6718938</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9720,7 +9715,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9730,7 +9725,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9757,45 +9752,55 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129465090</v>
+        <v>129465133</v>
       </c>
       <c r="B82" t="n">
-        <v>91998</v>
+        <v>56917</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>509695</v>
+        <v>509707</v>
       </c>
       <c r="R82" t="n">
-        <v>6718938</v>
+        <v>6719050</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9825,19 +9830,14 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>14:18</t>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Betade tallar 3 st</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9852,12 +9852,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9867,7 +9867,7 @@
         <v>129462748</v>
       </c>
       <c r="B83" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>129465440</v>
       </c>
       <c r="B88" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -7994,7 +7994,7 @@
         <v>129464365</v>
       </c>
       <c r="B66" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>129464423</v>
       </c>
       <c r="B69" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>129476786</v>
       </c>
       <c r="B70" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8540,50 +8540,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129459431</v>
+        <v>129457884</v>
       </c>
       <c r="B71" t="n">
-        <v>5177</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509267</v>
+        <v>509318</v>
       </c>
       <c r="R71" t="n">
-        <v>6718938</v>
+        <v>6718896</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8615,7 +8610,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8625,7 +8620,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8655,7 +8655,7 @@
         <v>129458905</v>
       </c>
       <c r="B72" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8758,45 +8758,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129457884</v>
+        <v>129459431</v>
       </c>
       <c r="B73" t="n">
-        <v>79044</v>
+        <v>5177</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>509318</v>
+        <v>509267</v>
       </c>
       <c r="R73" t="n">
-        <v>6718896</v>
+        <v>6718938</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8828,7 +8833,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8838,12 +8843,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8873,7 +8873,7 @@
         <v>129458644</v>
       </c>
       <c r="B74" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>129476788</v>
       </c>
       <c r="B76" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>129462456</v>
       </c>
       <c r="B77" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>129464986</v>
       </c>
       <c r="B78" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>129463357</v>
       </c>
       <c r="B80" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>129465090</v>
       </c>
       <c r="B81" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>129462748</v>
       </c>
       <c r="B83" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9970,10 +9970,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129462703</v>
+        <v>129463017</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9981,34 +9981,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>509520</v>
+        <v>509454</v>
       </c>
       <c r="R84" t="n">
-        <v>6719068</v>
+        <v>6719013</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10038,24 +10043,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10070,22 +10060,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129463017</v>
+        <v>129462703</v>
       </c>
       <c r="B85" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10093,39 +10083,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>509454</v>
+        <v>509520</v>
       </c>
       <c r="R85" t="n">
-        <v>6719013</v>
+        <v>6719068</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10155,9 +10140,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10172,12 +10172,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10391,7 +10391,7 @@
         <v>129465440</v>
       </c>
       <c r="B88" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -7991,32 +7991,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129464365</v>
+        <v>129464976</v>
       </c>
       <c r="B66" t="n">
-        <v>92003</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509739</v>
+        <v>509842</v>
       </c>
       <c r="R66" t="n">
-        <v>6718995</v>
+        <v>6718979</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8071,12 +8071,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8103,32 +8098,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129464976</v>
+        <v>129464365</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>92003</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8138,10 +8133,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509842</v>
+        <v>509739</v>
       </c>
       <c r="R67" t="n">
-        <v>6718979</v>
+        <v>6718995</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8173,7 +8168,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8183,7 +8178,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8540,48 +8540,57 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129457884</v>
+        <v>129458905</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509318</v>
+        <v>509314</v>
       </c>
       <c r="R71" t="n">
-        <v>6718896</v>
+        <v>6718886</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8608,24 +8617,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8640,69 +8634,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129458905</v>
+        <v>129457884</v>
       </c>
       <c r="B72" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509314</v>
+        <v>509318</v>
       </c>
       <c r="R72" t="n">
-        <v>6718886</v>
+        <v>6718896</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8729,9 +8714,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8746,12 +8746,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -7991,32 +7991,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129464976</v>
+        <v>129464365</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>92003</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509842</v>
+        <v>509739</v>
       </c>
       <c r="R66" t="n">
-        <v>6718979</v>
+        <v>6718995</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8071,7 +8071,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8098,45 +8103,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129464365</v>
+        <v>129458615</v>
       </c>
       <c r="B67" t="n">
-        <v>92003</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509739</v>
+        <v>509291</v>
       </c>
       <c r="R67" t="n">
-        <v>6718995</v>
+        <v>6718937</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8168,7 +8178,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8178,12 +8188,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8210,10 +8220,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129458615</v>
+        <v>129464976</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8221,39 +8231,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>509291</v>
+        <v>509842</v>
       </c>
       <c r="R68" t="n">
-        <v>6718937</v>
+        <v>6718979</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8285,7 +8290,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8295,12 +8300,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -10281,45 +10281,57 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129463311</v>
+        <v>129465440</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>509717</v>
+        <v>509588</v>
       </c>
       <c r="R87" t="n">
-        <v>6719091</v>
+        <v>6718900</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10349,96 +10361,75 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129465440</v>
+        <v>129463311</v>
       </c>
       <c r="B88" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>509588</v>
+        <v>509717</v>
       </c>
       <c r="R88" t="n">
-        <v>6718900</v>
+        <v>6719091</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10468,30 +10459,39 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -7994,7 +7994,7 @@
         <v>129464365</v>
       </c>
       <c r="B66" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>129464423</v>
       </c>
       <c r="B69" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>129476786</v>
       </c>
       <c r="B70" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>129458905</v>
       </c>
       <c r="B71" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>129458644</v>
       </c>
       <c r="B74" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>129476788</v>
       </c>
       <c r="B76" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>129462456</v>
       </c>
       <c r="B77" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>129464986</v>
       </c>
       <c r="B78" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>129463357</v>
       </c>
       <c r="B80" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>129465090</v>
       </c>
       <c r="B81" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>129462748</v>
       </c>
       <c r="B83" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9970,10 +9970,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129463017</v>
+        <v>129462703</v>
       </c>
       <c r="B84" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9981,39 +9981,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>509454</v>
+        <v>509520</v>
       </c>
       <c r="R84" t="n">
-        <v>6719013</v>
+        <v>6719068</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10043,9 +10038,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10060,22 +10070,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129462703</v>
+        <v>129463017</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10083,34 +10093,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>509520</v>
+        <v>509454</v>
       </c>
       <c r="R85" t="n">
-        <v>6719068</v>
+        <v>6719013</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10140,24 +10155,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10172,12 +10172,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10281,57 +10281,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129465440</v>
+        <v>129463311</v>
       </c>
       <c r="B87" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>509588</v>
+        <v>509717</v>
       </c>
       <c r="R87" t="n">
-        <v>6718900</v>
+        <v>6719091</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10361,75 +10349,96 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129463311</v>
+        <v>129465440</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>509717</v>
+        <v>509588</v>
       </c>
       <c r="R88" t="n">
-        <v>6719091</v>
+        <v>6718900</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10459,39 +10468,30 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -8103,10 +8103,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129458615</v>
+        <v>129464976</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8114,39 +8114,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509291</v>
+        <v>509842</v>
       </c>
       <c r="R67" t="n">
-        <v>6718937</v>
+        <v>6718979</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8178,7 +8173,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8188,12 +8183,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8220,10 +8210,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129464976</v>
+        <v>129458615</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8231,34 +8221,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>509842</v>
+        <v>509291</v>
       </c>
       <c r="R68" t="n">
-        <v>6718979</v>
+        <v>6718937</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8290,7 +8285,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8300,7 +8295,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8540,57 +8540,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129458905</v>
+        <v>129459431</v>
       </c>
       <c r="B71" t="n">
-        <v>98727</v>
+        <v>5177</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509314</v>
+        <v>509267</v>
       </c>
       <c r="R71" t="n">
-        <v>6718886</v>
+        <v>6718938</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8617,9 +8613,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8634,12 +8640,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8758,53 +8764,57 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129459431</v>
+        <v>129458905</v>
       </c>
       <c r="B73" t="n">
-        <v>5177</v>
+        <v>98727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>509267</v>
+        <v>509314</v>
       </c>
       <c r="R73" t="n">
-        <v>6718938</v>
+        <v>6718886</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8831,19 +8841,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8858,57 +8858,62 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129458644</v>
+        <v>129464831</v>
       </c>
       <c r="B74" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>509309</v>
+        <v>509874</v>
       </c>
       <c r="R74" t="n">
-        <v>6718945</v>
+        <v>6719068</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8940,7 +8945,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8950,7 +8955,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8977,50 +8987,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129464831</v>
+        <v>129458644</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>509874</v>
+        <v>509309</v>
       </c>
       <c r="R75" t="n">
-        <v>6719068</v>
+        <v>6718945</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9052,7 +9057,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9062,12 +9067,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, inte jätte gamla.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9538,45 +9538,55 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129463357</v>
+        <v>129465133</v>
       </c>
       <c r="B80" t="n">
-        <v>92006</v>
+        <v>56917</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>509719</v>
+        <v>509707</v>
       </c>
       <c r="R80" t="n">
-        <v>6719096</v>
+        <v>6719050</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9606,19 +9616,14 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>13:29</t>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Betade tallar 3 st</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9633,19 +9638,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129465090</v>
+        <v>129463357</v>
       </c>
       <c r="B81" t="n">
         <v>92006</v>
@@ -9680,10 +9685,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>509695</v>
+        <v>509719</v>
       </c>
       <c r="R81" t="n">
-        <v>6718938</v>
+        <v>6719096</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9715,7 +9720,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9725,7 +9730,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9752,55 +9757,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129465133</v>
+        <v>129465090</v>
       </c>
       <c r="B82" t="n">
-        <v>56917</v>
+        <v>92006</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>509707</v>
+        <v>509695</v>
       </c>
       <c r="R82" t="n">
-        <v>6719050</v>
+        <v>6718938</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9830,14 +9825,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Betade tallar 3 st</t>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9852,12 +9852,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129462703</v>
+        <v>129463017</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9981,34 +9981,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>509520</v>
+        <v>509454</v>
       </c>
       <c r="R84" t="n">
-        <v>6719068</v>
+        <v>6719013</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10038,24 +10043,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10070,22 +10060,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129463017</v>
+        <v>129462703</v>
       </c>
       <c r="B85" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10093,39 +10083,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>509454</v>
+        <v>509520</v>
       </c>
       <c r="R85" t="n">
-        <v>6719013</v>
+        <v>6719068</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10155,9 +10140,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10172,12 +10172,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10281,45 +10281,57 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129463311</v>
+        <v>129465440</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>509717</v>
+        <v>509588</v>
       </c>
       <c r="R87" t="n">
-        <v>6719091</v>
+        <v>6718900</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10349,96 +10361,75 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129465440</v>
+        <v>129463311</v>
       </c>
       <c r="B88" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>509588</v>
+        <v>509717</v>
       </c>
       <c r="R88" t="n">
-        <v>6718900</v>
+        <v>6719091</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10468,30 +10459,39 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7991,32 +7991,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129464365</v>
+        <v>129464976</v>
       </c>
       <c r="B66" t="n">
-        <v>92006</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509739</v>
+        <v>509842</v>
       </c>
       <c r="R66" t="n">
-        <v>6718995</v>
+        <v>6718979</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8071,12 +8071,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8103,10 +8098,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129464976</v>
+        <v>129458615</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8114,34 +8109,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509842</v>
+        <v>509291</v>
       </c>
       <c r="R67" t="n">
-        <v>6718979</v>
+        <v>6718937</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8183,7 +8183,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8210,50 +8215,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129458615</v>
+        <v>129464365</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>92006</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>509291</v>
+        <v>509739</v>
       </c>
       <c r="R68" t="n">
-        <v>6718937</v>
+        <v>6718995</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8540,53 +8540,57 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129459431</v>
+        <v>129458905</v>
       </c>
       <c r="B71" t="n">
-        <v>5177</v>
+        <v>98727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509267</v>
+        <v>509314</v>
       </c>
       <c r="R71" t="n">
-        <v>6718938</v>
+        <v>6718886</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8613,19 +8617,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8640,12 +8634,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8764,57 +8758,53 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129458905</v>
+        <v>129459431</v>
       </c>
       <c r="B73" t="n">
-        <v>98727</v>
+        <v>5177</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>509314</v>
+        <v>509267</v>
       </c>
       <c r="R73" t="n">
-        <v>6718886</v>
+        <v>6718938</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8841,9 +8831,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8858,12 +8858,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9538,55 +9538,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129465133</v>
+        <v>129463357</v>
       </c>
       <c r="B80" t="n">
-        <v>56917</v>
+        <v>92006</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>509707</v>
+        <v>509719</v>
       </c>
       <c r="R80" t="n">
-        <v>6719050</v>
+        <v>6719096</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9616,14 +9606,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Betade tallar 3 st</t>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9638,19 +9633,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129463357</v>
+        <v>129465090</v>
       </c>
       <c r="B81" t="n">
         <v>92006</v>
@@ -9685,10 +9680,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>509719</v>
+        <v>509695</v>
       </c>
       <c r="R81" t="n">
-        <v>6719096</v>
+        <v>6718938</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9720,7 +9715,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9730,7 +9725,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9757,45 +9752,55 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129465090</v>
+        <v>129465133</v>
       </c>
       <c r="B82" t="n">
-        <v>92006</v>
+        <v>56917</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>509695</v>
+        <v>509707</v>
       </c>
       <c r="R82" t="n">
-        <v>6718938</v>
+        <v>6719050</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9825,19 +9830,14 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>14:18</t>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Betade tallar 3 st</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9852,12 +9852,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129463017</v>
+        <v>129462703</v>
       </c>
       <c r="B84" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9981,39 +9981,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>509454</v>
+        <v>509520</v>
       </c>
       <c r="R84" t="n">
-        <v>6719013</v>
+        <v>6719068</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10043,9 +10038,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10060,22 +10070,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129462703</v>
+        <v>129463017</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10083,34 +10093,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>509520</v>
+        <v>509454</v>
       </c>
       <c r="R85" t="n">
-        <v>6719068</v>
+        <v>6719013</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10140,24 +10155,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10172,12 +10172,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10281,57 +10281,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129465440</v>
+        <v>129463311</v>
       </c>
       <c r="B87" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>509588</v>
+        <v>509717</v>
       </c>
       <c r="R87" t="n">
-        <v>6718900</v>
+        <v>6719091</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10361,75 +10349,96 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129463311</v>
+        <v>129465440</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>509717</v>
+        <v>509588</v>
       </c>
       <c r="R88" t="n">
-        <v>6719091</v>
+        <v>6718900</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10459,39 +10468,30 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10608,6 +10608,443 @@
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>129614129</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>509929</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6719024</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>129612442</v>
+      </c>
+      <c r="B91" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Långsberget, Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>509573</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6718880</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>129615757</v>
+      </c>
+      <c r="B92" t="n">
+        <v>92835</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>509783</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6719083</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129616377</v>
+      </c>
+      <c r="B93" t="n">
+        <v>81029</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>509702</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6719080</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -8098,50 +8098,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129458615</v>
+        <v>129464365</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>92006</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509291</v>
+        <v>509739</v>
       </c>
       <c r="R67" t="n">
-        <v>6718937</v>
+        <v>6718995</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8173,7 +8168,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8183,12 +8178,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8215,45 +8210,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129464365</v>
+        <v>129458615</v>
       </c>
       <c r="B68" t="n">
-        <v>92006</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>509739</v>
+        <v>509291</v>
       </c>
       <c r="R68" t="n">
-        <v>6718995</v>
+        <v>6718937</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8540,57 +8540,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129458905</v>
+        <v>129457884</v>
       </c>
       <c r="B71" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509314</v>
+        <v>509318</v>
       </c>
       <c r="R71" t="n">
-        <v>6718886</v>
+        <v>6718896</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8617,9 +8608,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8634,60 +8640,69 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129457884</v>
+        <v>129458905</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509318</v>
+        <v>509314</v>
       </c>
       <c r="R72" t="n">
-        <v>6718896</v>
+        <v>6718886</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8714,24 +8729,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8746,12 +8746,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8870,50 +8870,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129464831</v>
+        <v>129458644</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>509874</v>
+        <v>509309</v>
       </c>
       <c r="R74" t="n">
-        <v>6719068</v>
+        <v>6718945</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8945,7 +8940,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8955,12 +8950,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, inte jätte gamla.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8987,45 +8977,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129458644</v>
+        <v>129464831</v>
       </c>
       <c r="B75" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>509309</v>
+        <v>509874</v>
       </c>
       <c r="R75" t="n">
-        <v>6718945</v>
+        <v>6719068</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9057,7 +9052,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9067,7 +9062,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9538,7 +9538,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129463357</v>
+        <v>129465090</v>
       </c>
       <c r="B80" t="n">
         <v>92006</v>
@@ -9573,10 +9573,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>509719</v>
+        <v>509695</v>
       </c>
       <c r="R80" t="n">
-        <v>6719096</v>
+        <v>6718938</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9645,7 +9645,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129465090</v>
+        <v>129463357</v>
       </c>
       <c r="B81" t="n">
         <v>92006</v>
@@ -9680,10 +9680,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>509695</v>
+        <v>509719</v>
       </c>
       <c r="R81" t="n">
-        <v>6718938</v>
+        <v>6719096</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -7991,32 +7991,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129464976</v>
+        <v>129464365</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>92006</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509842</v>
+        <v>509739</v>
       </c>
       <c r="R66" t="n">
-        <v>6718979</v>
+        <v>6718995</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8071,7 +8071,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8098,32 +8103,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129464365</v>
+        <v>129464976</v>
       </c>
       <c r="B67" t="n">
-        <v>92006</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8133,10 +8138,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509739</v>
+        <v>509842</v>
       </c>
       <c r="R67" t="n">
-        <v>6718995</v>
+        <v>6718979</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8168,7 +8173,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8178,12 +8183,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8540,48 +8540,57 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129457884</v>
+        <v>129458905</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509318</v>
+        <v>509314</v>
       </c>
       <c r="R71" t="n">
-        <v>6718896</v>
+        <v>6718886</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8608,24 +8617,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8640,69 +8634,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129458905</v>
+        <v>129457884</v>
       </c>
       <c r="B72" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509314</v>
+        <v>509318</v>
       </c>
       <c r="R72" t="n">
-        <v>6718886</v>
+        <v>6718896</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8729,9 +8714,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8746,12 +8746,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -9538,7 +9538,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129465090</v>
+        <v>129463357</v>
       </c>
       <c r="B80" t="n">
         <v>92006</v>
@@ -9573,10 +9573,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>509695</v>
+        <v>509719</v>
       </c>
       <c r="R80" t="n">
-        <v>6718938</v>
+        <v>6719096</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9645,7 +9645,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129463357</v>
+        <v>129465090</v>
       </c>
       <c r="B81" t="n">
         <v>92006</v>
@@ -9680,10 +9680,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>509719</v>
+        <v>509695</v>
       </c>
       <c r="R81" t="n">
-        <v>6719096</v>
+        <v>6718938</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9970,10 +9970,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129462703</v>
+        <v>129463017</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9981,34 +9981,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>509520</v>
+        <v>509454</v>
       </c>
       <c r="R84" t="n">
-        <v>6719068</v>
+        <v>6719013</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10038,24 +10043,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10070,22 +10060,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129463017</v>
+        <v>129462703</v>
       </c>
       <c r="B85" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10093,39 +10083,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>509454</v>
+        <v>509520</v>
       </c>
       <c r="R85" t="n">
-        <v>6719013</v>
+        <v>6719068</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10155,9 +10140,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10172,12 +10172,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10281,45 +10281,57 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129463311</v>
+        <v>129465440</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>509717</v>
+        <v>509588</v>
       </c>
       <c r="R87" t="n">
-        <v>6719091</v>
+        <v>6718900</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10349,96 +10361,75 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129465440</v>
+        <v>129463311</v>
       </c>
       <c r="B88" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>509588</v>
+        <v>509717</v>
       </c>
       <c r="R88" t="n">
-        <v>6718900</v>
+        <v>6719091</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10468,30 +10459,39 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -7991,32 +7991,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129464365</v>
+        <v>129464976</v>
       </c>
       <c r="B66" t="n">
-        <v>92006</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509739</v>
+        <v>509842</v>
       </c>
       <c r="R66" t="n">
-        <v>6718995</v>
+        <v>6718979</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8071,12 +8071,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8103,32 +8098,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129464976</v>
+        <v>129464365</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>92006</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8138,10 +8133,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509842</v>
+        <v>509739</v>
       </c>
       <c r="R67" t="n">
-        <v>6718979</v>
+        <v>6718995</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8173,7 +8168,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8183,7 +8178,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8540,57 +8540,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129458905</v>
+        <v>129457884</v>
       </c>
       <c r="B71" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509314</v>
+        <v>509318</v>
       </c>
       <c r="R71" t="n">
-        <v>6718886</v>
+        <v>6718896</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8617,9 +8608,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8634,57 +8640,62 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129457884</v>
+        <v>129459431</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>5177</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509318</v>
+        <v>509267</v>
       </c>
       <c r="R72" t="n">
-        <v>6718896</v>
+        <v>6718938</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8716,7 +8727,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8726,12 +8737,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8758,53 +8764,57 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129459431</v>
+        <v>129458905</v>
       </c>
       <c r="B73" t="n">
-        <v>5177</v>
+        <v>98727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>509267</v>
+        <v>509314</v>
       </c>
       <c r="R73" t="n">
-        <v>6718938</v>
+        <v>6718886</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8831,19 +8841,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8858,12 +8858,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -10281,57 +10281,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129465440</v>
+        <v>129463311</v>
       </c>
       <c r="B87" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>509588</v>
+        <v>509717</v>
       </c>
       <c r="R87" t="n">
-        <v>6718900</v>
+        <v>6719091</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10361,75 +10349,96 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129463311</v>
+        <v>129465440</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>509717</v>
+        <v>509588</v>
       </c>
       <c r="R88" t="n">
-        <v>6719091</v>
+        <v>6718900</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10459,39 +10468,30 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -7991,10 +7991,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129464976</v>
+        <v>129458615</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8002,34 +8002,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509842</v>
+        <v>509291</v>
       </c>
       <c r="R66" t="n">
-        <v>6718979</v>
+        <v>6718937</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8061,7 +8066,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8071,7 +8076,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8098,32 +8108,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129464365</v>
+        <v>129464976</v>
       </c>
       <c r="B67" t="n">
-        <v>92006</v>
+        <v>79070</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8133,10 +8143,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509739</v>
+        <v>509842</v>
       </c>
       <c r="R67" t="n">
-        <v>6718995</v>
+        <v>6718979</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8168,7 +8178,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8178,12 +8188,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8210,50 +8215,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129458615</v>
+        <v>129464365</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>92034</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>509291</v>
+        <v>509739</v>
       </c>
       <c r="R68" t="n">
-        <v>6718937</v>
+        <v>6718995</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8330,7 +8330,7 @@
         <v>129464423</v>
       </c>
       <c r="B69" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>129476786</v>
       </c>
       <c r="B70" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8540,45 +8540,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129457884</v>
+        <v>129459431</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>5177</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509318</v>
+        <v>509267</v>
       </c>
       <c r="R71" t="n">
-        <v>6718896</v>
+        <v>6718938</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8610,7 +8615,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8620,12 +8625,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8652,50 +8652,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129459431</v>
+        <v>129457884</v>
       </c>
       <c r="B72" t="n">
-        <v>5177</v>
+        <v>79070</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509267</v>
+        <v>509318</v>
       </c>
       <c r="R72" t="n">
-        <v>6718938</v>
+        <v>6718896</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8727,7 +8722,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8737,7 +8732,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8767,7 +8767,7 @@
         <v>129458905</v>
       </c>
       <c r="B73" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>129458644</v>
       </c>
       <c r="B74" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>129464831</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>129476788</v>
       </c>
       <c r="B76" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>129462456</v>
       </c>
       <c r="B77" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>129464986</v>
       </c>
       <c r="B78" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>129460153</v>
       </c>
       <c r="B79" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9538,45 +9538,55 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129463357</v>
+        <v>129465133</v>
       </c>
       <c r="B80" t="n">
-        <v>92006</v>
+        <v>56920</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>509719</v>
+        <v>509707</v>
       </c>
       <c r="R80" t="n">
-        <v>6719096</v>
+        <v>6719050</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9606,19 +9616,14 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>13:29</t>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Betade tallar 3 st</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9633,22 +9638,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129465090</v>
+        <v>129463357</v>
       </c>
       <c r="B81" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9680,10 +9685,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>509695</v>
+        <v>509719</v>
       </c>
       <c r="R81" t="n">
-        <v>6718938</v>
+        <v>6719096</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9715,7 +9720,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9725,7 +9730,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9752,55 +9757,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129465133</v>
+        <v>129465090</v>
       </c>
       <c r="B82" t="n">
-        <v>56917</v>
+        <v>92034</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>509707</v>
+        <v>509695</v>
       </c>
       <c r="R82" t="n">
-        <v>6719050</v>
+        <v>6718938</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9830,14 +9825,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Betade tallar 3 st</t>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9852,12 +9852,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9867,7 +9867,7 @@
         <v>129462748</v>
       </c>
       <c r="B83" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9970,10 +9970,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129463017</v>
+        <v>129462703</v>
       </c>
       <c r="B84" t="n">
-        <v>57724</v>
+        <v>79070</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9981,39 +9981,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>509454</v>
+        <v>509520</v>
       </c>
       <c r="R84" t="n">
-        <v>6719013</v>
+        <v>6719068</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10043,9 +10038,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10060,22 +10070,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129462703</v>
+        <v>129463017</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10083,34 +10093,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>509520</v>
+        <v>509454</v>
       </c>
       <c r="R85" t="n">
-        <v>6719068</v>
+        <v>6719013</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10140,24 +10155,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10172,12 +10172,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10187,7 +10187,7 @@
         <v>129476790</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>129463311</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>129465440</v>
       </c>
       <c r="B88" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>129457466</v>
       </c>
       <c r="B89" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>129614129</v>
       </c>
       <c r="B90" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>129612442</v>
       </c>
       <c r="B91" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>129615757</v>
       </c>
       <c r="B92" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>129616377</v>
       </c>
       <c r="B93" t="n">
-        <v>81029</v>
+        <v>81055</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -9538,55 +9538,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129465133</v>
+        <v>129463357</v>
       </c>
       <c r="B80" t="n">
-        <v>56920</v>
+        <v>92034</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>509707</v>
+        <v>509719</v>
       </c>
       <c r="R80" t="n">
-        <v>6719050</v>
+        <v>6719096</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9616,14 +9606,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Betade tallar 3 st</t>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9638,19 +9633,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129463357</v>
+        <v>129465090</v>
       </c>
       <c r="B81" t="n">
         <v>92034</v>
@@ -9685,10 +9680,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>509719</v>
+        <v>509695</v>
       </c>
       <c r="R81" t="n">
-        <v>6719096</v>
+        <v>6718938</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9720,7 +9715,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9730,7 +9725,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9757,45 +9752,55 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129465090</v>
+        <v>129465133</v>
       </c>
       <c r="B82" t="n">
-        <v>92034</v>
+        <v>56920</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>509695</v>
+        <v>509707</v>
       </c>
       <c r="R82" t="n">
-        <v>6718938</v>
+        <v>6719050</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9825,19 +9830,14 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>14:18</t>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Betade tallar 3 st</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9852,12 +9852,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -10281,45 +10281,57 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129463311</v>
+        <v>129465440</v>
       </c>
       <c r="B87" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>509717</v>
+        <v>509588</v>
       </c>
       <c r="R87" t="n">
-        <v>6719091</v>
+        <v>6718900</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10349,96 +10361,75 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129465440</v>
+        <v>129463311</v>
       </c>
       <c r="B88" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>509588</v>
+        <v>509717</v>
       </c>
       <c r="R88" t="n">
-        <v>6718900</v>
+        <v>6719091</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10468,30 +10459,39 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -7991,50 +7991,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129458615</v>
+        <v>129464365</v>
       </c>
       <c r="B66" t="n">
-        <v>57730</v>
+        <v>92040</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509291</v>
+        <v>509739</v>
       </c>
       <c r="R66" t="n">
-        <v>6718937</v>
+        <v>6718995</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8066,7 +8061,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8076,12 +8071,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8111,7 +8106,7 @@
         <v>129464976</v>
       </c>
       <c r="B67" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8215,45 +8210,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129464365</v>
+        <v>129458615</v>
       </c>
       <c r="B68" t="n">
-        <v>92034</v>
+        <v>57735</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>509739</v>
+        <v>509291</v>
       </c>
       <c r="R68" t="n">
-        <v>6718995</v>
+        <v>6718937</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8330,7 +8330,7 @@
         <v>129464423</v>
       </c>
       <c r="B69" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>129476786</v>
       </c>
       <c r="B70" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8652,48 +8652,57 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129457884</v>
+        <v>129458905</v>
       </c>
       <c r="B72" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509318</v>
+        <v>509314</v>
       </c>
       <c r="R72" t="n">
-        <v>6718896</v>
+        <v>6718886</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8720,24 +8729,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8752,69 +8746,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129458905</v>
+        <v>129457884</v>
       </c>
       <c r="B73" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>509314</v>
+        <v>509318</v>
       </c>
       <c r="R73" t="n">
-        <v>6718886</v>
+        <v>6718896</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8841,9 +8826,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8858,57 +8858,62 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129458644</v>
+        <v>129464831</v>
       </c>
       <c r="B74" t="n">
-        <v>91545</v>
+        <v>57735</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>509309</v>
+        <v>509874</v>
       </c>
       <c r="R74" t="n">
-        <v>6718945</v>
+        <v>6719068</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8940,7 +8945,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8950,7 +8955,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8977,50 +8987,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129464831</v>
+        <v>129458644</v>
       </c>
       <c r="B75" t="n">
-        <v>57730</v>
+        <v>91551</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>509874</v>
+        <v>509309</v>
       </c>
       <c r="R75" t="n">
-        <v>6719068</v>
+        <v>6718945</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9052,7 +9057,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9062,12 +9067,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, inte jätte gamla.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9097,7 +9097,7 @@
         <v>129476788</v>
       </c>
       <c r="B76" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>129462456</v>
       </c>
       <c r="B77" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>129464986</v>
       </c>
       <c r="B78" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>129460153</v>
       </c>
       <c r="B79" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>129463357</v>
       </c>
       <c r="B80" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>129465090</v>
       </c>
       <c r="B81" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>129465133</v>
       </c>
       <c r="B82" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>129462748</v>
       </c>
       <c r="B83" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>129462703</v>
       </c>
       <c r="B84" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>129463017</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>129476790</v>
       </c>
       <c r="B86" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10281,57 +10281,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129465440</v>
+        <v>129463311</v>
       </c>
       <c r="B87" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>509588</v>
+        <v>509717</v>
       </c>
       <c r="R87" t="n">
-        <v>6718900</v>
+        <v>6719091</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10361,75 +10349,96 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129463311</v>
+        <v>129465440</v>
       </c>
       <c r="B88" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>509717</v>
+        <v>509588</v>
       </c>
       <c r="R88" t="n">
-        <v>6719091</v>
+        <v>6718900</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10459,39 +10468,30 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10501,7 +10501,7 @@
         <v>129457466</v>
       </c>
       <c r="B89" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>129614129</v>
       </c>
       <c r="B90" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>129612442</v>
       </c>
       <c r="B91" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>129615757</v>
       </c>
       <c r="B92" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>129616377</v>
       </c>
       <c r="B93" t="n">
-        <v>81055</v>
+        <v>81060</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -7994,7 +7994,7 @@
         <v>129464365</v>
       </c>
       <c r="B66" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8103,10 +8103,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129464976</v>
+        <v>129458615</v>
       </c>
       <c r="B67" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8114,34 +8114,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509842</v>
+        <v>509291</v>
       </c>
       <c r="R67" t="n">
-        <v>6718979</v>
+        <v>6718937</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8173,7 +8178,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8183,7 +8188,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8210,10 +8220,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129458615</v>
+        <v>129464976</v>
       </c>
       <c r="B68" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8221,39 +8231,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>509291</v>
+        <v>509842</v>
       </c>
       <c r="R68" t="n">
-        <v>6718937</v>
+        <v>6718979</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8285,7 +8290,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8295,12 +8300,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8330,7 +8330,7 @@
         <v>129464423</v>
       </c>
       <c r="B69" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>129476786</v>
       </c>
       <c r="B70" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8652,57 +8652,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129458905</v>
+        <v>129457884</v>
       </c>
       <c r="B72" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509314</v>
+        <v>509318</v>
       </c>
       <c r="R72" t="n">
-        <v>6718886</v>
+        <v>6718896</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8729,9 +8720,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8746,60 +8752,69 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129457884</v>
+        <v>129458905</v>
       </c>
       <c r="B73" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>509318</v>
+        <v>509314</v>
       </c>
       <c r="R73" t="n">
-        <v>6718896</v>
+        <v>6718886</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8826,24 +8841,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8858,62 +8858,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129464831</v>
+        <v>129458644</v>
       </c>
       <c r="B74" t="n">
-        <v>57735</v>
+        <v>91552</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>509874</v>
+        <v>509309</v>
       </c>
       <c r="R74" t="n">
-        <v>6719068</v>
+        <v>6718945</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8945,7 +8940,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8955,12 +8950,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, inte jätte gamla.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8987,45 +8977,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129458644</v>
+        <v>129464831</v>
       </c>
       <c r="B75" t="n">
-        <v>91551</v>
+        <v>57736</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>509309</v>
+        <v>509874</v>
       </c>
       <c r="R75" t="n">
-        <v>6718945</v>
+        <v>6719068</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9057,7 +9052,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9067,7 +9062,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9097,7 +9097,7 @@
         <v>129476788</v>
       </c>
       <c r="B76" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>129462456</v>
       </c>
       <c r="B77" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>129464986</v>
       </c>
       <c r="B78" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>129460153</v>
       </c>
       <c r="B79" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>129463357</v>
       </c>
       <c r="B80" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9645,45 +9645,55 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129465090</v>
+        <v>129465133</v>
       </c>
       <c r="B81" t="n">
-        <v>92040</v>
+        <v>56926</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>509695</v>
+        <v>509707</v>
       </c>
       <c r="R81" t="n">
-        <v>6718938</v>
+        <v>6719050</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9713,19 +9723,14 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>14:18</t>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Betade tallar 3 st</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9740,67 +9745,57 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129465133</v>
+        <v>129465090</v>
       </c>
       <c r="B82" t="n">
-        <v>56925</v>
+        <v>92041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>509707</v>
+        <v>509695</v>
       </c>
       <c r="R82" t="n">
-        <v>6719050</v>
+        <v>6718938</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9830,14 +9825,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Betade tallar 3 st</t>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9852,12 +9852,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9867,7 +9867,7 @@
         <v>129462748</v>
       </c>
       <c r="B83" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>129462703</v>
       </c>
       <c r="B84" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>129463017</v>
       </c>
       <c r="B85" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>129476790</v>
       </c>
       <c r="B86" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10281,45 +10281,57 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129463311</v>
+        <v>129465440</v>
       </c>
       <c r="B87" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>509717</v>
+        <v>509588</v>
       </c>
       <c r="R87" t="n">
-        <v>6719091</v>
+        <v>6718900</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10349,96 +10361,75 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129465440</v>
+        <v>129463311</v>
       </c>
       <c r="B88" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>509588</v>
+        <v>509717</v>
       </c>
       <c r="R88" t="n">
-        <v>6718900</v>
+        <v>6719091</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10468,30 +10459,39 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10501,7 +10501,7 @@
         <v>129457466</v>
       </c>
       <c r="B89" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>129614129</v>
       </c>
       <c r="B90" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>129612442</v>
       </c>
       <c r="B91" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>129615757</v>
       </c>
       <c r="B92" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>129616377</v>
       </c>
       <c r="B93" t="n">
-        <v>81060</v>
+        <v>81061</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -8652,48 +8652,57 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129457884</v>
+        <v>129458905</v>
       </c>
       <c r="B72" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509318</v>
+        <v>509314</v>
       </c>
       <c r="R72" t="n">
-        <v>6718896</v>
+        <v>6718886</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8720,24 +8729,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8752,69 +8746,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129458905</v>
+        <v>129457884</v>
       </c>
       <c r="B73" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>509314</v>
+        <v>509318</v>
       </c>
       <c r="R73" t="n">
-        <v>6718886</v>
+        <v>6718896</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8841,9 +8826,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8858,12 +8858,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9538,7 +9538,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129463357</v>
+        <v>129465090</v>
       </c>
       <c r="B80" t="n">
         <v>92041</v>
@@ -9573,10 +9573,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>509719</v>
+        <v>509695</v>
       </c>
       <c r="R80" t="n">
-        <v>6719096</v>
+        <v>6718938</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9645,55 +9645,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129465133</v>
+        <v>129463357</v>
       </c>
       <c r="B81" t="n">
-        <v>56926</v>
+        <v>92041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>509707</v>
+        <v>509719</v>
       </c>
       <c r="R81" t="n">
-        <v>6719050</v>
+        <v>6719096</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9723,14 +9713,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Betade tallar 3 st</t>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9745,57 +9740,67 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129465090</v>
+        <v>129465133</v>
       </c>
       <c r="B82" t="n">
-        <v>92041</v>
+        <v>56926</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>509695</v>
+        <v>509707</v>
       </c>
       <c r="R82" t="n">
-        <v>6718938</v>
+        <v>6719050</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9825,19 +9830,14 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>14:18</t>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Betade tallar 3 st</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9852,12 +9852,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -10281,57 +10281,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129465440</v>
+        <v>129463311</v>
       </c>
       <c r="B87" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>509588</v>
+        <v>509717</v>
       </c>
       <c r="R87" t="n">
-        <v>6718900</v>
+        <v>6719091</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10361,75 +10349,96 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129463311</v>
+        <v>129465440</v>
       </c>
       <c r="B88" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>509717</v>
+        <v>509588</v>
       </c>
       <c r="R88" t="n">
-        <v>6719091</v>
+        <v>6718900</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10459,39 +10468,30 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -7994,7 +7994,7 @@
         <v>129464365</v>
       </c>
       <c r="B66" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>129464976</v>
       </c>
       <c r="B68" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>129464423</v>
       </c>
       <c r="B69" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>129476786</v>
       </c>
       <c r="B70" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8540,50 +8540,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129459431</v>
+        <v>129457884</v>
       </c>
       <c r="B71" t="n">
-        <v>5177</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509267</v>
+        <v>509318</v>
       </c>
       <c r="R71" t="n">
-        <v>6718938</v>
+        <v>6718896</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8615,7 +8610,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8625,7 +8620,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8652,57 +8652,53 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129458905</v>
+        <v>129459431</v>
       </c>
       <c r="B72" t="n">
-        <v>98769</v>
+        <v>5177</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509314</v>
+        <v>509267</v>
       </c>
       <c r="R72" t="n">
-        <v>6718886</v>
+        <v>6718938</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8729,9 +8725,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8746,60 +8752,69 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129457884</v>
+        <v>129458905</v>
       </c>
       <c r="B73" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>509318</v>
+        <v>509314</v>
       </c>
       <c r="R73" t="n">
-        <v>6718896</v>
+        <v>6718886</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8826,24 +8841,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8858,12 +8858,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8873,7 +8873,7 @@
         <v>129458644</v>
       </c>
       <c r="B74" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>129476788</v>
       </c>
       <c r="B76" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>129462456</v>
       </c>
       <c r="B77" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>129464986</v>
       </c>
       <c r="B78" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>129460153</v>
       </c>
       <c r="B79" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9538,45 +9538,55 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129465090</v>
+        <v>129465133</v>
       </c>
       <c r="B80" t="n">
-        <v>92041</v>
+        <v>56926</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>509695</v>
+        <v>509707</v>
       </c>
       <c r="R80" t="n">
-        <v>6718938</v>
+        <v>6719050</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9606,19 +9616,14 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>14:18</t>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Betade tallar 3 st</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9633,12 +9638,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9648,7 +9653,7 @@
         <v>129463357</v>
       </c>
       <c r="B81" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9752,55 +9757,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129465133</v>
+        <v>129465090</v>
       </c>
       <c r="B82" t="n">
-        <v>56926</v>
+        <v>92046</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>509707</v>
+        <v>509695</v>
       </c>
       <c r="R82" t="n">
-        <v>6719050</v>
+        <v>6718938</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9830,14 +9825,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Betade tallar 3 st</t>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9852,12 +9852,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9867,7 +9867,7 @@
         <v>129462748</v>
       </c>
       <c r="B83" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>129462703</v>
       </c>
       <c r="B84" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>129476790</v>
       </c>
       <c r="B86" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>129463311</v>
       </c>
       <c r="B87" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>129465440</v>
       </c>
       <c r="B88" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>129457466</v>
       </c>
       <c r="B89" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>129614129</v>
       </c>
       <c r="B90" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>129612442</v>
       </c>
       <c r="B91" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>129615757</v>
       </c>
       <c r="B92" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>129616377</v>
       </c>
       <c r="B93" t="n">
-        <v>81061</v>
+        <v>81066</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -7991,45 +7991,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129464365</v>
+        <v>129458615</v>
       </c>
       <c r="B66" t="n">
-        <v>92046</v>
+        <v>57736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509739</v>
+        <v>509291</v>
       </c>
       <c r="R66" t="n">
-        <v>6718995</v>
+        <v>6718937</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8061,7 +8066,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8071,12 +8076,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8103,50 +8108,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129458615</v>
+        <v>129464365</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>92046</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509291</v>
+        <v>509739</v>
       </c>
       <c r="R67" t="n">
-        <v>6718937</v>
+        <v>6718995</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8540,45 +8540,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129457884</v>
+        <v>129459431</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>5177</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509318</v>
+        <v>509267</v>
       </c>
       <c r="R71" t="n">
-        <v>6718896</v>
+        <v>6718938</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8610,7 +8615,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8620,12 +8625,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8652,53 +8652,57 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129459431</v>
+        <v>129458905</v>
       </c>
       <c r="B72" t="n">
-        <v>5177</v>
+        <v>98774</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509267</v>
+        <v>509314</v>
       </c>
       <c r="R72" t="n">
-        <v>6718938</v>
+        <v>6718886</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8725,19 +8729,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8752,69 +8746,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129458905</v>
+        <v>129457884</v>
       </c>
       <c r="B73" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>509314</v>
+        <v>509318</v>
       </c>
       <c r="R73" t="n">
-        <v>6718886</v>
+        <v>6718896</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8841,9 +8826,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8858,12 +8858,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9538,55 +9538,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129465133</v>
+        <v>129465090</v>
       </c>
       <c r="B80" t="n">
-        <v>56926</v>
+        <v>92046</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>509707</v>
+        <v>509695</v>
       </c>
       <c r="R80" t="n">
-        <v>6719050</v>
+        <v>6718938</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9616,14 +9606,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Betade tallar 3 st</t>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9638,12 +9633,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9757,45 +9752,55 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129465090</v>
+        <v>129465133</v>
       </c>
       <c r="B82" t="n">
-        <v>92046</v>
+        <v>56926</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>509695</v>
+        <v>509707</v>
       </c>
       <c r="R82" t="n">
-        <v>6718938</v>
+        <v>6719050</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9825,19 +9830,14 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>14:18</t>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Betade tallar 3 st</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9852,12 +9852,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -7991,50 +7991,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129458615</v>
+        <v>129464365</v>
       </c>
       <c r="B66" t="n">
-        <v>57736</v>
+        <v>92046</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509291</v>
+        <v>509739</v>
       </c>
       <c r="R66" t="n">
-        <v>6718937</v>
+        <v>6718995</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8066,7 +8061,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8076,12 +8071,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8108,45 +8103,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129464365</v>
+        <v>129458615</v>
       </c>
       <c r="B67" t="n">
-        <v>92046</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509739</v>
+        <v>509291</v>
       </c>
       <c r="R67" t="n">
-        <v>6718995</v>
+        <v>6718937</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8540,53 +8540,57 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129459431</v>
+        <v>129458905</v>
       </c>
       <c r="B71" t="n">
-        <v>5177</v>
+        <v>98774</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509267</v>
+        <v>509314</v>
       </c>
       <c r="R71" t="n">
-        <v>6718938</v>
+        <v>6718886</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8613,19 +8617,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8640,69 +8634,65 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129458905</v>
+        <v>129459431</v>
       </c>
       <c r="B72" t="n">
-        <v>98774</v>
+        <v>5177</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509314</v>
+        <v>509267</v>
       </c>
       <c r="R72" t="n">
-        <v>6718886</v>
+        <v>6718938</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8729,9 +8719,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8746,12 +8746,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -9538,45 +9538,55 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129465090</v>
+        <v>129465133</v>
       </c>
       <c r="B80" t="n">
-        <v>92046</v>
+        <v>56926</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>509695</v>
+        <v>509707</v>
       </c>
       <c r="R80" t="n">
-        <v>6718938</v>
+        <v>6719050</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9606,19 +9616,14 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>14:18</t>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Betade tallar 3 st</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9633,12 +9638,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9752,55 +9757,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129465133</v>
+        <v>129465090</v>
       </c>
       <c r="B82" t="n">
-        <v>56926</v>
+        <v>92046</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>509707</v>
+        <v>509695</v>
       </c>
       <c r="R82" t="n">
-        <v>6719050</v>
+        <v>6718938</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9830,14 +9825,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Betade tallar 3 st</t>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9852,12 +9852,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -7991,32 +7991,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129464365</v>
+        <v>129464976</v>
       </c>
       <c r="B66" t="n">
-        <v>92046</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509739</v>
+        <v>509842</v>
       </c>
       <c r="R66" t="n">
-        <v>6718995</v>
+        <v>6718979</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8071,12 +8071,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8220,32 +8215,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129464976</v>
+        <v>129464365</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>92046</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8255,10 +8250,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>509842</v>
+        <v>509739</v>
       </c>
       <c r="R68" t="n">
-        <v>6718979</v>
+        <v>6718995</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8290,7 +8285,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8300,7 +8295,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8540,57 +8540,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129458905</v>
+        <v>129459431</v>
       </c>
       <c r="B71" t="n">
-        <v>98774</v>
+        <v>5177</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509314</v>
+        <v>509267</v>
       </c>
       <c r="R71" t="n">
-        <v>6718886</v>
+        <v>6718938</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8617,9 +8613,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8634,62 +8640,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129459431</v>
+        <v>129457884</v>
       </c>
       <c r="B72" t="n">
-        <v>5177</v>
+        <v>79081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509267</v>
+        <v>509318</v>
       </c>
       <c r="R72" t="n">
-        <v>6718938</v>
+        <v>6718896</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8721,7 +8722,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8731,7 +8732,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8758,48 +8764,57 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129457884</v>
+        <v>129458905</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>509318</v>
+        <v>509314</v>
       </c>
       <c r="R73" t="n">
-        <v>6718896</v>
+        <v>6718886</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8826,24 +8841,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8858,57 +8858,62 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129458644</v>
+        <v>129464831</v>
       </c>
       <c r="B74" t="n">
-        <v>91557</v>
+        <v>57736</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>509309</v>
+        <v>509874</v>
       </c>
       <c r="R74" t="n">
-        <v>6718945</v>
+        <v>6719068</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8940,7 +8945,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8950,7 +8955,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8977,50 +8987,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129464831</v>
+        <v>129458644</v>
       </c>
       <c r="B75" t="n">
-        <v>57736</v>
+        <v>91557</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>509874</v>
+        <v>509309</v>
       </c>
       <c r="R75" t="n">
-        <v>6719068</v>
+        <v>6718945</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9052,7 +9057,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9062,12 +9067,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, inte jätte gamla.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -7991,10 +7991,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129464976</v>
+        <v>129458615</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8002,34 +8002,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>509842</v>
+        <v>509291</v>
       </c>
       <c r="R66" t="n">
-        <v>6718979</v>
+        <v>6718937</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8061,7 +8066,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8071,7 +8076,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8098,50 +8108,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129458615</v>
+        <v>129464365</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>92050</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>509291</v>
+        <v>509739</v>
       </c>
       <c r="R67" t="n">
-        <v>6718937</v>
+        <v>6718995</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8173,7 +8178,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8183,12 +8188,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8215,32 +8220,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129464365</v>
+        <v>129464976</v>
       </c>
       <c r="B68" t="n">
-        <v>92046</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8250,10 +8255,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>509739</v>
+        <v>509842</v>
       </c>
       <c r="R68" t="n">
-        <v>6718995</v>
+        <v>6718979</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8285,7 +8290,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8295,12 +8300,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8330,7 +8330,7 @@
         <v>129464423</v>
       </c>
       <c r="B69" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>129476786</v>
       </c>
       <c r="B70" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8540,50 +8540,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129459431</v>
+        <v>129457884</v>
       </c>
       <c r="B71" t="n">
-        <v>5177</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509267</v>
+        <v>509318</v>
       </c>
       <c r="R71" t="n">
-        <v>6718938</v>
+        <v>6718896</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8615,7 +8610,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8625,7 +8620,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8652,45 +8652,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129457884</v>
+        <v>129459431</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>5177</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509318</v>
+        <v>509267</v>
       </c>
       <c r="R72" t="n">
-        <v>6718896</v>
+        <v>6718938</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8722,7 +8727,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8732,12 +8737,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8767,7 +8767,7 @@
         <v>129458905</v>
       </c>
       <c r="B73" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>129458644</v>
       </c>
       <c r="B75" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>129476788</v>
       </c>
       <c r="B76" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>129462456</v>
       </c>
       <c r="B77" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>129464986</v>
       </c>
       <c r="B78" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>129463357</v>
       </c>
       <c r="B81" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>129465090</v>
       </c>
       <c r="B82" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>129462748</v>
       </c>
       <c r="B83" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10281,45 +10281,57 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129463311</v>
+        <v>129465440</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>509717</v>
+        <v>509588</v>
       </c>
       <c r="R87" t="n">
-        <v>6719091</v>
+        <v>6718900</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10349,96 +10361,75 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129465440</v>
+        <v>129463311</v>
       </c>
       <c r="B88" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>509588</v>
+        <v>509717</v>
       </c>
       <c r="R88" t="n">
-        <v>6718900</v>
+        <v>6719091</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10468,30 +10459,39 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10720,7 +10720,7 @@
         <v>129612442</v>
       </c>
       <c r="B91" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>129615757</v>
       </c>
       <c r="B92" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -8111,7 +8111,7 @@
         <v>129464365</v>
       </c>
       <c r="B67" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>129464423</v>
       </c>
       <c r="B69" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>129476786</v>
       </c>
       <c r="B70" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8540,48 +8540,57 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129457884</v>
+        <v>129458905</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>509318</v>
+        <v>509314</v>
       </c>
       <c r="R71" t="n">
-        <v>6718896</v>
+        <v>6718886</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8608,24 +8617,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8640,62 +8634,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129459431</v>
+        <v>129457884</v>
       </c>
       <c r="B72" t="n">
-        <v>5177</v>
+        <v>79081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>509267</v>
+        <v>509318</v>
       </c>
       <c r="R72" t="n">
-        <v>6718938</v>
+        <v>6718896</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8727,7 +8716,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8737,7 +8726,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8764,57 +8758,53 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129458905</v>
+        <v>129459431</v>
       </c>
       <c r="B73" t="n">
-        <v>98778</v>
+        <v>5177</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>509314</v>
+        <v>509267</v>
       </c>
       <c r="R73" t="n">
-        <v>6718886</v>
+        <v>6718938</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8841,9 +8831,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8858,62 +8858,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129464831</v>
+        <v>129458644</v>
       </c>
       <c r="B74" t="n">
-        <v>57736</v>
+        <v>91563</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>509874</v>
+        <v>509309</v>
       </c>
       <c r="R74" t="n">
-        <v>6719068</v>
+        <v>6718945</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8945,7 +8940,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8955,12 +8950,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, inte jätte gamla.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8987,45 +8977,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129458644</v>
+        <v>129464831</v>
       </c>
       <c r="B75" t="n">
-        <v>91561</v>
+        <v>57736</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>509309</v>
+        <v>509874</v>
       </c>
       <c r="R75" t="n">
-        <v>6718945</v>
+        <v>6719068</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9057,7 +9052,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9067,7 +9062,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, inte jätte gamla.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9097,7 +9097,7 @@
         <v>129476788</v>
       </c>
       <c r="B76" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>129462456</v>
       </c>
       <c r="B77" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>129464986</v>
       </c>
       <c r="B78" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9538,55 +9538,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129465133</v>
+        <v>129463357</v>
       </c>
       <c r="B80" t="n">
-        <v>56926</v>
+        <v>92052</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>509707</v>
+        <v>509719</v>
       </c>
       <c r="R80" t="n">
-        <v>6719050</v>
+        <v>6719096</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9616,14 +9606,19 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Betade tallar 3 st</t>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9638,22 +9633,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129463357</v>
+        <v>129465090</v>
       </c>
       <c r="B81" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9685,10 +9680,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>509719</v>
+        <v>509695</v>
       </c>
       <c r="R81" t="n">
-        <v>6719096</v>
+        <v>6718938</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9720,7 +9715,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9730,7 +9725,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9757,45 +9752,55 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129465090</v>
+        <v>129465133</v>
       </c>
       <c r="B82" t="n">
-        <v>92050</v>
+        <v>56926</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>509695</v>
+        <v>509707</v>
       </c>
       <c r="R82" t="n">
-        <v>6718938</v>
+        <v>6719050</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9825,19 +9830,14 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>14:18</t>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Betade tallar 3 st</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9852,12 +9852,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9867,7 +9867,7 @@
         <v>129462748</v>
       </c>
       <c r="B83" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10281,57 +10281,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129465440</v>
+        <v>129463311</v>
       </c>
       <c r="B87" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>509588</v>
+        <v>509717</v>
       </c>
       <c r="R87" t="n">
-        <v>6718900</v>
+        <v>6719091</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10361,75 +10349,96 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129463311</v>
+        <v>129465440</v>
       </c>
       <c r="B88" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lindbergsmyran, Lindbergsmyran, Dlr</t>
+          <t>Lindbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>509717</v>
+        <v>509588</v>
       </c>
       <c r="R88" t="n">
-        <v>6719091</v>
+        <v>6718900</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10459,39 +10468,30 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10720,7 +10720,7 @@
         <v>129612442</v>
       </c>
       <c r="B91" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>129615757</v>
       </c>
       <c r="B92" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -9970,10 +9970,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129462703</v>
+        <v>129463017</v>
       </c>
       <c r="B84" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9981,34 +9981,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>509520</v>
+        <v>509454</v>
       </c>
       <c r="R84" t="n">
-        <v>6719068</v>
+        <v>6719013</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10038,24 +10043,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10070,22 +10060,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129463017</v>
+        <v>129462703</v>
       </c>
       <c r="B85" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10093,39 +10083,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>509454</v>
+        <v>509520</v>
       </c>
       <c r="R85" t="n">
-        <v>6719013</v>
+        <v>6719068</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10155,9 +10140,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10172,12 +10172,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -9970,10 +9970,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129463017</v>
+        <v>129462703</v>
       </c>
       <c r="B84" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9981,39 +9981,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Långsberget, Dlr</t>
+          <t>Långsberget, Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>509454</v>
+        <v>509520</v>
       </c>
       <c r="R84" t="n">
-        <v>6719013</v>
+        <v>6719068</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10043,9 +10038,24 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10060,22 +10070,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Johan Hedberg</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129462703</v>
+        <v>129463017</v>
       </c>
       <c r="B85" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10083,34 +10093,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Långsberget, Långsberget, Dlr</t>
+          <t>Långsberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>509520</v>
+        <v>509454</v>
       </c>
       <c r="R85" t="n">
-        <v>6719068</v>
+        <v>6719013</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10140,24 +10155,9 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10172,12 +10172,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Johan Hedberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -10720,7 +10720,7 @@
         <v>129612442</v>
       </c>
       <c r="B91" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11045,6 +11045,117 @@
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129961939</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>509807</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6718971</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -10613,7 +10613,7 @@
         <v>129614129</v>
       </c>
       <c r="B90" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>129612442</v>
       </c>
       <c r="B91" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>129615757</v>
       </c>
       <c r="B92" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>129616377</v>
       </c>
       <c r="B93" t="n">
-        <v>81066</v>
+        <v>81069</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -10613,7 +10613,7 @@
         <v>129614129</v>
       </c>
       <c r="B90" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>129612442</v>
       </c>
       <c r="B91" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>129615757</v>
       </c>
       <c r="B92" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>129616377</v>
       </c>
       <c r="B93" t="n">
-        <v>81069</v>
+        <v>81072</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>129961939</v>
       </c>
       <c r="B94" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -11050,7 +11050,7 @@
         <v>129961939</v>
       </c>
       <c r="B94" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -11050,7 +11050,7 @@
         <v>129961939</v>
       </c>
       <c r="B94" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -11050,7 +11050,7 @@
         <v>129961939</v>
       </c>
       <c r="B94" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AY131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11156,6 +11156,3780 @@
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>130964396</v>
+      </c>
+      <c r="B95" t="n">
+        <v>98906</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>509365</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6718883</v>
+      </c>
+      <c r="S95" t="n">
+        <v>15</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Betydande förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>130964535</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>509939</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6719007</v>
+      </c>
+      <c r="S96" t="n">
+        <v>15</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Flera . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>130964529</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>509588</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6719099</v>
+      </c>
+      <c r="S97" t="n">
+        <v>15</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Enstaka . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>130964573</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>509515</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6719063</v>
+      </c>
+      <c r="S98" t="n">
+        <v>15</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Måttliga förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>130964540</v>
+      </c>
+      <c r="B99" t="n">
+        <v>98906</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>509850</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6719013</v>
+      </c>
+      <c r="S99" t="n">
+        <v>15</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Flera . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>130964531</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>509889</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6719134</v>
+      </c>
+      <c r="S100" t="n">
+        <v>15</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Flera . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>130964543</v>
+      </c>
+      <c r="B101" t="n">
+        <v>57861</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>509622</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6718933</v>
+      </c>
+      <c r="S101" t="n">
+        <v>15</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Födosökspår . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>130964526</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>509610</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6719050</v>
+      </c>
+      <c r="S102" t="n">
+        <v>15</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Enstaka . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>130964547</v>
+      </c>
+      <c r="B103" t="n">
+        <v>57861</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>509495</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6718877</v>
+      </c>
+      <c r="S103" t="n">
+        <v>15</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Födosökspår . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>130964545</v>
+      </c>
+      <c r="B104" t="n">
+        <v>57053</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>509535</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6718925</v>
+      </c>
+      <c r="S104" t="n">
+        <v>15</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Spillning . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>130964541</v>
+      </c>
+      <c r="B105" t="n">
+        <v>91784</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>509703</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6719018</v>
+      </c>
+      <c r="S105" t="n">
+        <v>15</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Enstaka . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>130964642</v>
+      </c>
+      <c r="B106" t="n">
+        <v>99012</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>509917</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6719042</v>
+      </c>
+      <c r="S106" t="n">
+        <v>15</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Måttliga förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>130964537</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>509822</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6718960</v>
+      </c>
+      <c r="S107" t="n">
+        <v>15</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Rikligt . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>130964574</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>509667</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6719184</v>
+      </c>
+      <c r="S108" t="n">
+        <v>15</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Måttliga förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>130964647</v>
+      </c>
+      <c r="B109" t="n">
+        <v>92082</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>658</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>509741</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6718998</v>
+      </c>
+      <c r="S109" t="n">
+        <v>15</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Måttliga förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>130964641</v>
+      </c>
+      <c r="B110" t="n">
+        <v>98906</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>509932</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6719045</v>
+      </c>
+      <c r="S110" t="n">
+        <v>15</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Måttlig förekomst . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>130964544</v>
+      </c>
+      <c r="B111" t="n">
+        <v>57053</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>509543</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6718926</v>
+      </c>
+      <c r="S111" t="n">
+        <v>15</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Spillning . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>130964650</v>
+      </c>
+      <c r="B112" t="n">
+        <v>92243</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>509694</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6718936</v>
+      </c>
+      <c r="S112" t="n">
+        <v>15</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Måttliga förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>130964533</v>
+      </c>
+      <c r="B113" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>509984</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6719028</v>
+      </c>
+      <c r="S113" t="n">
+        <v>15</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Rikligt . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>130964645</v>
+      </c>
+      <c r="B114" t="n">
+        <v>99012</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>509804</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6719024</v>
+      </c>
+      <c r="S114" t="n">
+        <v>15</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Måttliga förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>130964539</v>
+      </c>
+      <c r="B115" t="n">
+        <v>98906</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>509808</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6719041</v>
+      </c>
+      <c r="S115" t="n">
+        <v>15</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Flera . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>130964527</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>509597</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6719076</v>
+      </c>
+      <c r="S116" t="n">
+        <v>15</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Rikligt . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>130964534</v>
+      </c>
+      <c r="B117" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>509979</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6719017</v>
+      </c>
+      <c r="S117" t="n">
+        <v>15</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Flera . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>130964651</v>
+      </c>
+      <c r="B118" t="n">
+        <v>98906</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>509585</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6719030</v>
+      </c>
+      <c r="S118" t="n">
+        <v>15</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Måttlig förekomst . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>130964649</v>
+      </c>
+      <c r="B119" t="n">
+        <v>98906</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>509705</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6718923</v>
+      </c>
+      <c r="S119" t="n">
+        <v>15</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Måttlig förekomst . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>130964648</v>
+      </c>
+      <c r="B120" t="n">
+        <v>92243</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>509744</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6718982</v>
+      </c>
+      <c r="S120" t="n">
+        <v>15</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Måttliga förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>130964536</v>
+      </c>
+      <c r="B121" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>509940</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6719001</v>
+      </c>
+      <c r="S121" t="n">
+        <v>15</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Flera . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>130964644</v>
+      </c>
+      <c r="B122" t="n">
+        <v>98893</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>509801</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6719017</v>
+      </c>
+      <c r="S122" t="n">
+        <v>15</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Sparsamma förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>130964542</v>
+      </c>
+      <c r="B123" t="n">
+        <v>57053</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>509635</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6718941</v>
+      </c>
+      <c r="S123" t="n">
+        <v>15</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Spillning . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>130964640</v>
+      </c>
+      <c r="B124" t="n">
+        <v>57861</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>509697</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6719144</v>
+      </c>
+      <c r="S124" t="n">
+        <v>15</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Gamla födosöksspår . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>130964643</v>
+      </c>
+      <c r="B125" t="n">
+        <v>98906</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>509829</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6719000</v>
+      </c>
+      <c r="S125" t="n">
+        <v>15</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Måttlig förekomst . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>130964390</v>
+      </c>
+      <c r="B126" t="n">
+        <v>98989</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>509475</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6718881</v>
+      </c>
+      <c r="S126" t="n">
+        <v>15</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Måttliga förekomster, Ca 10-15 plantor . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>130964538</v>
+      </c>
+      <c r="B127" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>509875</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6719025</v>
+      </c>
+      <c r="S127" t="n">
+        <v>15</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Enstaka . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>130964546</v>
+      </c>
+      <c r="B128" t="n">
+        <v>92479</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>898</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>509515</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6718886</v>
+      </c>
+      <c r="S128" t="n">
+        <v>15</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Betydande förekomst . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>130964639</v>
+      </c>
+      <c r="B129" t="n">
+        <v>57053</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>509645</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6719169</v>
+      </c>
+      <c r="S129" t="n">
+        <v>15</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Vinterspillning . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>130964646</v>
+      </c>
+      <c r="B130" t="n">
+        <v>91784</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>509764</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6719043</v>
+      </c>
+      <c r="S130" t="n">
+        <v>15</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Måttliga förekomster . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130964532</v>
+      </c>
+      <c r="B131" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Långsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>509952</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6719064</v>
+      </c>
+      <c r="S131" t="n">
+        <v>15</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Rikligt . inventering åt vasa vind</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Pia Edfors, Anna Sjövall, Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51820-2025 artfynd.xlsx
+++ b/artfynd/A 51820-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY151"/>
+  <dimension ref="A1:AZ151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98447121</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98447125</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124896106</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124892061</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124892464</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124892791</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128490340</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128491489</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,6 +1679,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98447115</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1761,6 +1811,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124891582</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1873,6 +1928,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486887</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1970,6 +2030,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476798</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2086,6 +2151,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464423</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2188,6 +2258,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964647</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2310,6 +2385,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128488726</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2412,6 +2492,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964546</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2519,6 +2604,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129616377</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2626,6 +2716,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124895869</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2733,6 +2828,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124896719</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2840,6 +2940,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124897616</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2962,6 +3067,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486195</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3059,6 +3169,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476785</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3161,6 +3276,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964541</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3263,6 +3383,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964646</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3370,6 +3495,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124897606</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3477,6 +3607,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129463357</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3589,6 +3724,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464365</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3696,6 +3836,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129465090</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3793,6 +3938,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476786</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3895,6 +4045,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964648</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3997,6 +4152,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964650</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4104,6 +4264,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124898009</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4226,6 +4391,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124897229</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4333,6 +4503,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486877</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4440,6 +4615,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128488978</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4552,6 +4732,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128490267</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4659,6 +4844,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128490404</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4775,6 +4965,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129615757</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4877,6 +5072,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1276517</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4999,6 +5199,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124895984</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5106,6 +5311,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124896716</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5228,6 +5438,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486700</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5335,6 +5550,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128487458</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5442,6 +5662,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128489884</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5549,6 +5774,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129458644</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5656,6 +5886,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129461622</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5762,6 +5997,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476788</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5859,6 +6099,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98447122</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5966,6 +6211,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124894688</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6073,6 +6323,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124894734</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6180,6 +6435,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124895315</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6287,6 +6547,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124895425</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6394,6 +6659,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124896240</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6501,6 +6771,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124896513</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6608,6 +6883,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124896599</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6715,6 +6995,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124896896</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6822,6 +7107,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128490161</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6934,6 +7224,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129457466</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7046,6 +7341,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129457625</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7158,6 +7458,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129457884</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7270,6 +7575,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129459532</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7376,6 +7686,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129460153</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7488,6 +7803,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129462703</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7595,6 +7915,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129463311</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7702,6 +8027,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464976</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7799,6 +8129,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476790</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7906,6 +8241,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129614129</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8017,6 +8357,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129961939</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8119,6 +8464,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964378</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8221,6 +8571,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964397</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8323,6 +8678,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964441</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8425,6 +8785,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964526</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8527,6 +8892,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964527</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8629,6 +8999,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964529</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8731,6 +9106,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964530</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8833,6 +9213,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964531</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8935,6 +9320,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964532</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9037,6 +9427,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964533</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9139,6 +9534,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964534</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9241,6 +9641,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964535</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9343,6 +9748,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964536</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9445,6 +9855,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964537</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9547,6 +9962,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964538</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9649,6 +10069,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964573</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9751,6 +10176,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964574</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9863,6 +10293,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128490219</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9965,6 +10400,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1965225</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10067,6 +10507,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1965226</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10188,6 +10633,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124872024</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10300,6 +10750,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129457219</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10402,6 +10857,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129463017</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10504,6 +10964,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964377</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10606,6 +11071,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964543</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10708,6 +11178,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964547</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10810,6 +11285,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964640</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10935,6 +11415,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104468758</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11047,6 +11532,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124896415</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11164,6 +11654,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129458615</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11281,6 +11776,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464831</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11401,6 +11901,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128490921</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11521,6 +12026,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122450852</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11638,6 +12148,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116633511</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11755,6 +12270,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116633545</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11872,6 +12392,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116633699</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11989,6 +12514,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116634091</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12101,6 +12631,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116634144</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12213,6 +12748,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116634267</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12325,6 +12865,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116634547</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12442,6 +12987,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116634611</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12559,6 +13109,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116634715</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12671,6 +13226,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116634789</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12788,6 +13348,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116634900</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12905,6 +13470,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116635024</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13017,6 +13587,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116635330</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13134,6 +13709,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116635410</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13251,6 +13831,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124893148</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13363,6 +13948,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124893781</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13479,6 +14069,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128490570</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13591,6 +14186,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129465133</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13693,6 +14293,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964542</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13795,6 +14400,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964544</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13897,6 +14507,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964545</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13999,6 +14614,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964639</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14111,6 +14731,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124891555</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14223,6 +14848,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129459431</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14325,6 +14955,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98447119</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14442,6 +15077,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124784369</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14554,6 +15194,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124892413</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14666,6 +15311,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124893576</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14768,6 +15418,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964396</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14870,6 +15525,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964440</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14972,6 +15632,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964539</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15074,6 +15739,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964540</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15176,6 +15846,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964641</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15278,6 +15953,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964643</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15380,6 +16060,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964649</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15482,6 +16167,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964651</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15584,6 +16274,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964644</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15690,6 +16385,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129458905</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15816,6 +16516,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129462456</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15922,6 +16627,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129462748</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16028,6 +16738,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464986</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16138,6 +16853,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129465440</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16245,6 +16965,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129612442</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16347,6 +17072,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964390</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16449,6 +17179,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964642</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16551,6 +17286,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130964645</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16653,6 +17393,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6559324</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16755,6 +17500,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6559325</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16871,8 +17621,165 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129457998</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>